--- a/reports/telegram/aegis_india_2026-09-08.xlsx
+++ b/reports/telegram/aegis_india_2026-09-08.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -527,220 +527,91 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>🔎 WHY NEW=0 · 228 scored · 16 already in CURRENT · biggest blocker: model disagreement (198) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Engine</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>Stop State</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Dist to Stop %</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>Max Loss if Stop %</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>Position ID</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>GNFC</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE+</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>553.3</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>591.25</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>570.8357</v>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>587.67</v>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-GNFC-20260806-03d0a7</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>CHAMBLFERT</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE+</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>452.35</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>419.35</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>403.5857</v>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>-10.78</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>477.49</v>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -752,12 +623,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -767,17 +638,17 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>397</v>
+        <v>553.3</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>421.75</v>
+        <v>591.25</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>6.23</v>
+        <v>6.86</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -785,7 +656,7 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>386.4571</v>
+        <v>570.8357</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
@@ -793,22 +664,22 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>8.369999999999999</v>
+        <v>3.45</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-2.66</v>
+        <v>3.17</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>412.81</v>
+        <v>587.67</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+          <t>IND-R2-GNFC-20260806-03d0a7</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -820,12 +691,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -839,13 +710,13 @@
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>389.85</v>
+        <v>452.35</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>410.05</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>5.18</v>
+        <v>419.35</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-7.3</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
@@ -853,7 +724,7 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>378.3286</v>
+        <v>403.5857</v>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
@@ -861,22 +732,22 @@
         </is>
       </c>
       <c r="L9" s="4" t="n">
-        <v>7.74</v>
+        <v>3.76</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.96</v>
+        <v>-10.78</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>407.13</v>
+        <v>477.49</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BEL-20260804-c9f4d0</t>
+          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -888,7 +759,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -903,17 +774,17 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>417.6</v>
+        <v>397</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>421.2</v>
+        <v>421.75</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.86</v>
+        <v>6.23</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
@@ -921,7 +792,7 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>407.3714</v>
+        <v>386.4571</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -929,17 +800,17 @@
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.28</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.45</v>
+        <v>-2.66</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>432.94</v>
+        <v>412.81</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -956,7 +827,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -971,17 +842,17 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>187.46</v>
+        <v>389.85</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>185.6</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>-0.99</v>
+        <v>410.05</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>5.18</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
@@ -989,7 +860,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>181.8114</v>
+        <v>378.3286</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
@@ -997,17 +868,17 @@
         </is>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.04</v>
+        <v>7.74</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.01</v>
+        <v>-2.96</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>195.93</v>
+        <v>407.13</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
+          <t>IND-R1-BEL-20260804-c9f4d0</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
@@ -1024,7 +895,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1039,17 +910,17 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1413.5</v>
+        <v>417.6</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1390</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>-1.66</v>
+        <v>421.2</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.86</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
@@ -1057,7 +928,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>1382.3857</v>
+        <v>407.3714</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
@@ -1065,17 +936,17 @@
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.55</v>
+        <v>3.28</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.2</v>
+        <v>-2.45</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1460.17</v>
+        <v>432.94</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-CIPLA-20260828-d46712</t>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -1092,7 +963,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1107,17 +978,17 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>1449.5</v>
+        <v>187.46</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1416.3</v>
+        <v>185.6</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-2.29</v>
+        <v>-0.99</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
@@ -1125,7 +996,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1412.0571</v>
+        <v>181.8114</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
@@ -1133,17 +1004,17 @@
         </is>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.3</v>
+        <v>2.04</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.58</v>
+        <v>-3.01</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1505.66</v>
+        <v>195.93</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
+          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
@@ -1160,7 +1031,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1175,17 +1046,17 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>239.45</v>
+        <v>1413.5</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>233.47</v>
+        <v>1390</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-2.5</v>
+        <v>-1.66</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
@@ -1193,7 +1064,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>232.2186</v>
+        <v>1382.3857</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -1201,17 +1072,17 @@
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.02</v>
+        <v>-2.2</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>250.3</v>
+        <v>1460.17</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ONGC-20260811-326ea2</t>
+          <t>IND-R1-CIPLA-20260828-d46712</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -1228,7 +1099,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1243,17 +1114,17 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1191</v>
+        <v>1449.5</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1151.9</v>
+        <v>1416.3</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-3.28</v>
+        <v>-2.29</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -1261,7 +1132,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1149.2286</v>
+        <v>1412.0571</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
@@ -1269,17 +1140,17 @@
         </is>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.51</v>
+        <v>-2.58</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1253.66</v>
+        <v>1505.66</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ZYDUSLIFE-20260811-58636b</t>
+          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
@@ -1296,32 +1167,32 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>113.36</v>
+        <v>239.45</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>116.19</v>
-      </c>
-      <c r="H16" s="5" t="n">
-        <v>2.5</v>
+        <v>233.47</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-2.5</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -1329,7 +1200,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>111.9314</v>
+        <v>232.2186</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -1337,22 +1208,22 @@
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.67</v>
+        <v>0.54</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.26</v>
+        <v>-3.02</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>118.87</v>
+        <v>250.3</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R1-ONGC-20260811-326ea2</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1364,32 +1235,32 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5499</v>
+        <v>1191</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5519.5</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>0.37</v>
+        <v>1151.9</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-3.28</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -1397,7 +1268,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>5265.5714</v>
+        <v>1149.2286</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
@@ -1405,22 +1276,22 @@
         </is>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.6</v>
+        <v>0.23</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-4.24</v>
+        <v>-3.51</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>5954.25</v>
+        <v>1253.66</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R1-ZYDUSLIFE-20260811-58636b</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1303,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1447,17 +1318,17 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2744.3</v>
+        <v>113.36</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2654.2</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>-3.28</v>
+        <v>116.19</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>2.5</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -1465,7 +1336,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2556.9857</v>
+        <v>111.9314</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
@@ -1473,22 +1344,22 @@
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.83</v>
+        <v>-1.26</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2949.97</v>
+        <v>118.87</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>ROTATED_SAMEDAY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1371,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1519,13 +1390,13 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>11475</v>
+        <v>5499</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>11005</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>-4.1</v>
+        <v>5519.5</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0.37</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -1533,7 +1404,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>10569.1429</v>
+        <v>5265.5714</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
@@ -1541,17 +1412,17 @@
         </is>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.96</v>
+        <v>4.6</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-7.89</v>
+        <v>-4.24</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>11970.43</v>
+        <v>5954.25</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
@@ -1568,7 +1439,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1583,17 +1454,17 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>709</v>
+        <v>2744.3</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>665.7</v>
+        <v>2654.2</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-6.11</v>
+        <v>-3.28</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -1601,7 +1472,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>643.1072</v>
+        <v>2556.9857</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -1609,22 +1480,22 @@
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.39</v>
+        <v>3.66</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-9.289999999999999</v>
+        <v>-6.83</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>749.16</v>
+        <v>2949.97</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>ROTATED_SAMEDAY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>ROTATED_SAMEDAY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1636,143 +1507,288 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>11475</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>11005</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>10569.1429</v>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>-7.89</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>11970.43</v>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>HOLD · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>709</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>665.7</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-6.11</v>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>643.1072</v>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M22" s="4" t="n">
+        <v>-9.289999999999999</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>749.16</v>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>ROTATED_SAMEDAY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
           <t>ITC</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F23" s="4" t="n">
         <v>284.85</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>263.3</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H23" s="6" t="n">
         <v>-7.57</v>
       </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="n">
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="n">
         <v>255.5857</v>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="L23" s="4" t="n">
         <v>2.93</v>
       </c>
-      <c r="M21" s="4" t="n">
+      <c r="M23" s="4" t="n">
         <v>-10.27</v>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="N23" s="4" t="n">
         <v>297.98</v>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>IND-R2-ITC-20260804-e0ebbb</t>
         </is>
       </c>
-      <c r="P21" s="4" t="inlineStr">
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
           <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
+    <mergeCell ref="A5:P5"/>
     <mergeCell ref="A28:P28"/>
     <mergeCell ref="A32:P32"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A27:P27"/>
     <mergeCell ref="A31:P31"/>
+    <mergeCell ref="A34:P34"/>
+    <mergeCell ref="A35:P35"/>
     <mergeCell ref="A4:P4"/>
     <mergeCell ref="A30:P30"/>
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A26:P26"/>
     <mergeCell ref="A29:P29"/>
-    <mergeCell ref="A25:P25"/>
-    <mergeCell ref="A24:P24"/>
+    <mergeCell ref="A33:P33"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/telegram/aegis_india_2026-09-08.xlsx
+++ b/reports/telegram/aegis_india_2026-09-08.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -508,14 +508,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>16 investable · NEW 0 · ACTIVE+ 10 · ACTIVE 6   ·   R2 8 · MOMENTUM 0 · R1 8 (advisory)</t>
+          <t>18 investable · NEW 2 · ACTIVE+ 10 · ACTIVE 6   ·   R2 10 · MOMENTUM 0 · R1 8 (advisory)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 16 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.36% from entry, worst single -10.78%</t>
+          <t>🛡 DOWNSIDE · 18 position(s) with an INTACT stop · if all of them fired today the average outcome is -4.25% from entry, worst single -10.57%</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 WHY NEW=0 · 228 scored · 16 already in CURRENT · biggest blocker: model disagreement (198) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 NEW=2 · 228 scored · 18 already in CURRENT · biggest blocker: model disagreement (196) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -633,22 +633,22 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>553.3</v>
+        <v>117.05</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>591.25</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>6.86</v>
+        <v>117.05</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>570.8357</v>
+        <v>113.8</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
@@ -664,22 +664,22 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.45</v>
+        <v>2.78</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>3.17</v>
+        <v>-2.78</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>587.67</v>
+        <v>121.93</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-GNFC-20260806-03d0a7</t>
+          <t>IND-R2-IEX-20260908-d0ae28</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -701,22 +701,22 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>452.35</v>
+        <v>233.86</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>419.35</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>-7.3</v>
+        <v>233.86</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>403.5857</v>
+        <v>226.5271</v>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
@@ -732,22 +732,22 @@
         </is>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.76</v>
+        <v>3.14</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-10.78</v>
+        <v>-3.14</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>477.49</v>
+        <v>244.86</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
+          <t>IND-R2-JIOFIN-20260908-9bbbc2</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>397</v>
+        <v>553.3</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>421.75</v>
+        <v>591.25</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>6.23</v>
+        <v>6.86</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>386.4571</v>
+        <v>565.6214</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -800,22 +800,22 @@
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>8.369999999999999</v>
+        <v>4.33</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.66</v>
+        <v>2.23</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>412.81</v>
+        <v>587.67</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
+          <t>IND-R2-GNFC-20260806-03d0a7</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>389.85</v>
+        <v>452.35</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>410.05</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>5.18</v>
+        <v>419.35</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-7.3</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>378.3286</v>
+        <v>404.55</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
@@ -868,22 +868,22 @@
         </is>
       </c>
       <c r="L11" s="4" t="n">
-        <v>7.74</v>
+        <v>3.53</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.96</v>
+        <v>-10.57</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>407.13</v>
+        <v>477.49</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-BEL-20260804-c9f4d0</t>
+          <t>IND-R2-CHAMBLFERT-20260804-893fdf</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -910,17 +910,17 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>417.6</v>
+        <v>397</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>421.2</v>
+        <v>421.75</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.86</v>
+        <v>6.23</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>407.3714</v>
+        <v>386.4571</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
@@ -936,17 +936,17 @@
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.28</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.45</v>
+        <v>-2.66</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>432.94</v>
+        <v>412.81</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-COALINDIA-20260805-9349c5</t>
+          <t>IND-R1-KOTAKBANK-20260804-4429c0</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -978,17 +978,17 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>187.46</v>
+        <v>389.85</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>185.6</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>-0.99</v>
+        <v>410.05</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>5.18</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>181.8114</v>
+        <v>378.3286</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
@@ -1004,17 +1004,17 @@
         </is>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2.04</v>
+        <v>7.74</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-3.01</v>
+        <v>-2.96</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>195.93</v>
+        <v>407.13</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
+          <t>IND-R1-BEL-20260804-c9f4d0</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1413.5</v>
+        <v>417.6</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1390</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>-1.66</v>
+        <v>421.2</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.86</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1382.3857</v>
+        <v>407.3714</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -1072,17 +1072,17 @@
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.55</v>
+        <v>3.28</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.2</v>
+        <v>-2.45</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1460.17</v>
+        <v>432.94</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-CIPLA-20260828-d46712</t>
+          <t>IND-R1-COALINDIA-20260805-9349c5</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1449.5</v>
+        <v>187.46</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1416.3</v>
+        <v>185.6</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-2.29</v>
+        <v>-0.99</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1412.0571</v>
+        <v>181.8114</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
@@ -1140,17 +1140,17 @@
         </is>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3</v>
+        <v>2.04</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.58</v>
+        <v>-3.01</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1505.66</v>
+        <v>195.93</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
+          <t>IND-R1-TATASTEEL-20260828-c215bb</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>239.45</v>
+        <v>1413.5</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>233.47</v>
+        <v>1390</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>-2.5</v>
+        <v>-1.66</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>232.2186</v>
+        <v>1382.3857</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -1208,17 +1208,17 @@
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-3.02</v>
+        <v>-2.2</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>250.3</v>
+        <v>1460.17</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ONGC-20260811-326ea2</t>
+          <t>IND-R1-CIPLA-20260828-d46712</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1250,17 +1250,17 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1191</v>
+        <v>1449.5</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1151.9</v>
+        <v>1416.3</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>-3.28</v>
+        <v>-2.29</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1149.2286</v>
+        <v>1412.0571</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
@@ -1276,17 +1276,17 @@
         </is>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-3.51</v>
+        <v>-2.58</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>1253.66</v>
+        <v>1505.66</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>IND-R1-ZYDUSLIFE-20260811-58636b</t>
+          <t>IND-R1-ICICIBANK-20260804-abc7f8</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
@@ -1303,32 +1303,32 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>113.36</v>
+        <v>239.45</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>116.19</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>2.5</v>
+        <v>233.47</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>-2.5</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>111.9314</v>
+        <v>232.2186</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
@@ -1344,22 +1344,22 @@
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.67</v>
+        <v>0.54</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.26</v>
+        <v>-3.02</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>118.87</v>
+        <v>250.3</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PNB-20260804-ffee9e</t>
+          <t>IND-R1-ONGC-20260811-326ea2</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1371,32 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5499</v>
+        <v>1191</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>5519.5</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>0.37</v>
+        <v>1151.9</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-3.28</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>5265.5714</v>
+        <v>1149.2286</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
@@ -1412,22 +1412,22 @@
         </is>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.6</v>
+        <v>0.23</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-4.24</v>
+        <v>-3.51</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>5954.25</v>
+        <v>1253.66</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
+          <t>IND-R1-ZYDUSLIFE-20260811-58636b</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1454,17 +1454,17 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2744.3</v>
+        <v>113.36</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2654.2</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>-3.28</v>
+        <v>116.19</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>2.5</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2556.9857</v>
+        <v>112.5514</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -1480,22 +1480,22 @@
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.66</v>
+        <v>3.13</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-6.83</v>
+        <v>-0.71</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2949.97</v>
+        <v>118.87</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
+          <t>IND-R2-PNB-20260804-ffee9e</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>ROTATED_SAMEDAY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>11475</v>
+        <v>5499</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>11005</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>-4.1</v>
+        <v>5519.5</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0.37</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>10569.1429</v>
+        <v>5251.9286</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
@@ -1548,17 +1548,17 @@
         </is>
       </c>
       <c r="L21" s="4" t="n">
-        <v>3.96</v>
+        <v>4.85</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-7.89</v>
+        <v>-4.49</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>11970.43</v>
+        <v>5954.25</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
+          <t>IND-R2-PERSISTENT-20260805-fc13a0</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>709</v>
+        <v>2744.3</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>665.7</v>
+        <v>2654.2</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>-6.11</v>
+        <v>-3.28</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>643.1072</v>
+        <v>2542.2</v>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
@@ -1616,22 +1616,22 @@
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>3.39</v>
+        <v>4.22</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-9.289999999999999</v>
+        <v>-7.36</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>749.16</v>
+        <v>2949.97</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
+          <t>IND-R2-TIINDIA-20260805-7e40ba</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>ROTATED_SAMEDAY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>ROTATED_SAMEDAY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1643,131 +1643,267 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>11475</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>11005</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>10630.4286</v>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M23" s="4" t="n">
+        <v>-7.36</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>11970.43</v>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-BAJAJHLDNG-20260805-b3d435</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>HOLD · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>709</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>665.7</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>-6.11</v>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>639.9857</v>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>-9.73</v>
+      </c>
+      <c r="N24" s="4" t="n">
+        <v>749.16</v>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>IND-R2-BATAINDIA-20260804-a68e4b</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>ROTATED_SAMEDAY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
           <t>ITC</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F25" s="4" t="n">
         <v>284.85</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>263.3</v>
       </c>
-      <c r="H23" s="6" t="n">
+      <c r="H25" s="6" t="n">
         <v>-7.57</v>
       </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>255.5857</v>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>255.8714</v>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L23" s="4" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v>-10.27</v>
-      </c>
-      <c r="N23" s="4" t="n">
+      <c r="L25" s="4" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="M25" s="4" t="n">
+        <v>-10.17</v>
+      </c>
+      <c r="N25" s="4" t="n">
         <v>297.98</v>
       </c>
-      <c r="O23" s="4" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>IND-R2-ITC-20260804-e0ebbb</t>
         </is>
       </c>
-      <c r="P23" s="4" t="inlineStr">
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
@@ -1778,15 +1914,15 @@
     <mergeCell ref="A5:P5"/>
     <mergeCell ref="A28:P28"/>
     <mergeCell ref="A32:P32"/>
+    <mergeCell ref="A36:P36"/>
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A27:P27"/>
+    <mergeCell ref="A37:P37"/>
     <mergeCell ref="A31:P31"/>
     <mergeCell ref="A34:P34"/>
     <mergeCell ref="A35:P35"/>
     <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A3:P3"/>
     <mergeCell ref="A30:P30"/>
-    <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A26:P26"/>
     <mergeCell ref="A29:P29"/>
     <mergeCell ref="A33:P33"/>
     <mergeCell ref="A2:P2"/>
